--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -83,7 +83,7 @@
     <t>英灵一层</t>
   </si>
   <si>
-    <t>黄巾小兵</t>
+    <t>波才</t>
   </si>
   <si>
     <t>10000</t>
@@ -92,7 +92,7 @@
     <t>英灵二层</t>
   </si>
   <si>
-    <t>黄巾队长</t>
+    <t>张曼成</t>
   </si>
   <si>
     <t>50000</t>
@@ -101,7 +101,7 @@
     <t>英灵三层</t>
   </si>
   <si>
-    <t>黄巾首领</t>
+    <t>程远志</t>
   </si>
   <si>
     <t>200000</t>
@@ -110,7 +110,7 @@
     <t>英灵四层</t>
   </si>
   <si>
-    <t>黄巾将军</t>
+    <t>马元义</t>
   </si>
   <si>
     <t>500000</t>
@@ -154,7 +154,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,14 +164,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -644,133 +636,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -782,10 +774,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1123,12 +1115,13 @@
     <col min="4" max="5" width="17.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="11.625" style="3" customWidth="1"/>
     <col min="7" max="7" width="17" style="3" customWidth="1"/>
-    <col min="8" max="9" width="19.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="3" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.83333333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="8" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.08333333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.5" style="2" customWidth="1"/>
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1768,7 +1761,6 @@
     </row>
     <row r="23" customHeight="1" spans="6:18">
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="8"/>
@@ -1808,10 +1800,13 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 C3:D5 F3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E9" r:id="rId1" display="马元义" tooltip="https://baike.baidu.com/item/%E9%A9%AC%E5%85%83%E4%B9%89/2282194?fromModule=lemma_inlink"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -95,7 +95,7 @@
     <t>张曼成</t>
   </si>
   <si>
-    <t>50000</t>
+    <t>40000</t>
   </si>
   <si>
     <t>英灵三层</t>
@@ -104,7 +104,7 @@
     <t>程远志</t>
   </si>
   <si>
-    <t>200000</t>
+    <t>100000</t>
   </si>
   <si>
     <t>英灵四层</t>
@@ -113,7 +113,7 @@
     <t>马元义</t>
   </si>
   <si>
-    <t>500000</t>
+    <t>300000</t>
   </si>
   <si>
     <t>英灵五层</t>
@@ -140,7 +140,7 @@
     <t>张角</t>
   </si>
   <si>
-    <t>6000000</t>
+    <t>10000000</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H7" s="7">
         <f t="shared" si="0"/>
-        <v>100000000</v>
+        <v>80000000</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ref="I7:I13" si="1">I6+40</f>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H8" s="7">
         <f t="shared" si="0"/>
-        <v>600000000</v>
+        <v>300000000</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="1"/>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="H9" s="7">
         <f t="shared" si="0"/>
-        <v>2000000000</v>
+        <v>1200000000</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="1"/>
@@ -1477,14 +1477,14 @@
         <v>29</v>
       </c>
       <c r="F10" s="7">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="G10" s="7">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="H10" s="7">
         <f t="shared" si="0"/>
-        <v>5000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="1"/>
@@ -1569,14 +1569,14 @@
         <v>33</v>
       </c>
       <c r="F12" s="7">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="G12" s="7">
-        <v>4000000</v>
+        <v>5000000</v>
       </c>
       <c r="H12" s="7">
         <f t="shared" si="0"/>
-        <v>28000000000</v>
+        <v>35000000000</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="1"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H13" s="7">
         <f t="shared" si="0"/>
-        <v>48000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="1"/>
@@ -1800,7 +1800,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="N3:N5 C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
   <si>
     <t>#</t>
   </si>
@@ -44,6 +44,9 @@
     <t>MonsterName</t>
   </si>
   <si>
+    <t>Require</t>
+  </si>
+  <si>
     <t>Attr</t>
   </si>
   <si>
@@ -138,9 +141,6 @@
   </si>
   <si>
     <t>张角</t>
-  </si>
-  <si>
-    <t>10000000</t>
   </si>
 </sst>
 </file>
@@ -154,7 +154,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +164,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -636,137 +642,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -784,6 +790,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1106,64 +1115,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="17.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="17" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="3" customWidth="1"/>
-    <col min="9" max="9" width="13.1666666666667" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.83333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.08333333333333" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.5" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="17" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="3" customWidth="1"/>
+    <col min="10" max="10" width="13.1666666666667" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.83333333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8" style="2" customWidth="1"/>
+    <col min="14" max="14" width="7.08333333333333" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.5" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="2"/>
+      <c r="J1" s="4"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
-      <c r="Q1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O1" s="2"/>
       <c r="R1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="2"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="Q2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="O2" s="2"/>
       <c r="R2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="S2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1175,7 +1185,7 @@
       <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="6" t="s">
@@ -1187,7 +1197,7 @@
       <c r="I3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="5" t="s">
@@ -1202,12 +1212,15 @@
       <c r="N3" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="O3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
@@ -1215,7 +1228,7 @@
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
@@ -1227,7 +1240,7 @@
       <c r="I4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
       <c r="K4" s="5" t="s">
@@ -1242,76 +1255,82 @@
       <c r="N4" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="O4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="K5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="N5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:18">
+        <v>15</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:19">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="7">
-        <f t="shared" ref="H6:H13" si="0">G6*Q6*1000</f>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="7">
+        <f t="shared" ref="I6:I13" si="0">H6*R6*1000</f>
         <v>10000000</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="7">
         <v>40</v>
       </c>
-      <c r="J6" s="8">
+      <c r="K6" s="8">
         <v>100</v>
       </c>
-      <c r="K6" s="8">
-        <v>1800</v>
-      </c>
       <c r="L6" s="8">
         <v>1800</v>
       </c>
@@ -1319,45 +1338,48 @@
         <v>1800</v>
       </c>
       <c r="N6" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O6" s="8">
         <v>99</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="R6" s="8">
         <v>1</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:18">
+    <row r="7" customHeight="1" spans="1:19">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="7">
+      <c r="F7" s="1">
+        <v>100</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="7">
         <f t="shared" si="0"/>
         <v>80000000</v>
       </c>
-      <c r="I7" s="7">
-        <f t="shared" ref="I7:I13" si="1">I6+40</f>
+      <c r="J7" s="7">
+        <f t="shared" ref="J7:J13" si="1">J6+40</f>
         <v>80</v>
       </c>
-      <c r="J7" s="8">
+      <c r="K7" s="8">
         <v>100</v>
       </c>
-      <c r="K7" s="8">
-        <v>1800</v>
-      </c>
       <c r="L7" s="8">
         <v>1800</v>
       </c>
@@ -1365,45 +1387,48 @@
         <v>1800</v>
       </c>
       <c r="N7" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O7" s="8">
         <v>99</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="R7" s="8">
         <v>2</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>2000</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:18">
+    <row r="8" customHeight="1" spans="1:19">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="7">
+      <c r="F8" s="1">
+        <v>200</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="7">
         <f t="shared" si="0"/>
         <v>300000000</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="7">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="J8" s="8">
+      <c r="K8" s="8">
         <v>100</v>
       </c>
-      <c r="K8" s="8">
-        <v>1800</v>
-      </c>
       <c r="L8" s="8">
         <v>1800</v>
       </c>
@@ -1411,45 +1436,48 @@
         <v>1800</v>
       </c>
       <c r="N8" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O8" s="8">
         <v>99</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="R8" s="8">
         <v>3</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>4000</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:18">
+    <row r="9" customHeight="1" spans="1:19">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="F9" s="1">
+        <v>400</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="7">
         <f t="shared" si="0"/>
         <v>1200000000</v>
       </c>
-      <c r="I9" s="7">
+      <c r="J9" s="7">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="J9" s="8">
+      <c r="K9" s="8">
         <v>100</v>
       </c>
-      <c r="K9" s="8">
-        <v>1800</v>
-      </c>
       <c r="L9" s="8">
         <v>1800</v>
       </c>
@@ -1457,45 +1485,48 @@
         <v>1800</v>
       </c>
       <c r="N9" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O9" s="8">
         <v>99</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="R9" s="8">
         <v>4</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>8000</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:18">
+    <row r="10" customHeight="1" spans="1:19">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="7">
-        <v>800000</v>
+        <v>30</v>
+      </c>
+      <c r="F10" s="1">
+        <v>600</v>
       </c>
       <c r="G10" s="7">
         <v>800000</v>
       </c>
       <c r="H10" s="7">
+        <v>800000</v>
+      </c>
+      <c r="I10" s="7">
         <f t="shared" si="0"/>
         <v>4000000000</v>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="J10" s="8">
+      <c r="K10" s="8">
         <v>100</v>
       </c>
-      <c r="K10" s="8">
-        <v>1800</v>
-      </c>
       <c r="L10" s="8">
         <v>1800</v>
       </c>
@@ -1503,45 +1534,48 @@
         <v>1800</v>
       </c>
       <c r="N10" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O10" s="8">
         <v>99</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="R10" s="8">
         <v>5</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <v>16000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:18">
+    <row r="11" customHeight="1" spans="1:19">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="7">
-        <v>2000000</v>
+        <v>32</v>
+      </c>
+      <c r="F11" s="1">
+        <v>800</v>
       </c>
       <c r="G11" s="7">
-        <v>2000000</v>
+        <v>1600000</v>
       </c>
       <c r="H11" s="7">
+        <v>1600000</v>
+      </c>
+      <c r="I11" s="7">
         <f t="shared" si="0"/>
-        <v>12000000000</v>
-      </c>
-      <c r="I11" s="7">
+        <v>9600000000</v>
+      </c>
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="J11" s="8">
+      <c r="K11" s="8">
         <v>100</v>
       </c>
-      <c r="K11" s="8">
-        <v>1800</v>
-      </c>
       <c r="L11" s="8">
         <v>1800</v>
       </c>
@@ -1549,45 +1583,48 @@
         <v>1800</v>
       </c>
       <c r="N11" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O11" s="8">
         <v>99</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="R11" s="8">
         <v>6</v>
       </c>
-      <c r="R11" s="2">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:18">
+      <c r="S11" s="2">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:19">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="7">
-        <v>5000000</v>
+        <v>34</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1000</v>
       </c>
       <c r="G12" s="7">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
       <c r="H12" s="7">
+        <v>3000000</v>
+      </c>
+      <c r="I12" s="7">
         <f t="shared" si="0"/>
-        <v>35000000000</v>
-      </c>
-      <c r="I12" s="7">
+        <v>21000000000</v>
+      </c>
+      <c r="J12" s="7">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="J12" s="8">
+      <c r="K12" s="8">
         <v>100</v>
       </c>
-      <c r="K12" s="8">
-        <v>1800</v>
-      </c>
       <c r="L12" s="8">
         <v>1800</v>
       </c>
@@ -1595,45 +1632,48 @@
         <v>1800</v>
       </c>
       <c r="N12" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O12" s="8">
         <v>99</v>
       </c>
-      <c r="Q12" s="8">
+      <c r="R12" s="8">
         <v>7</v>
       </c>
-      <c r="R12" s="2">
-        <v>64000</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:18">
+      <c r="S12" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:19">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>36</v>
+      <c r="F13" s="1">
+        <v>1500</v>
+      </c>
+      <c r="G13" s="7">
+        <v>5000000</v>
       </c>
       <c r="H13" s="7">
+        <v>5000000</v>
+      </c>
+      <c r="I13" s="7">
         <f t="shared" si="0"/>
-        <v>80000000000</v>
-      </c>
-      <c r="I13" s="7">
+        <v>40000000000</v>
+      </c>
+      <c r="J13" s="7">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="J13" s="8">
+      <c r="K13" s="8">
         <v>100</v>
       </c>
-      <c r="K13" s="8">
-        <v>1800</v>
-      </c>
       <c r="L13" s="8">
         <v>1800</v>
       </c>
@@ -1641,166 +1681,169 @@
         <v>1800</v>
       </c>
       <c r="N13" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O13" s="8">
         <v>99</v>
       </c>
-      <c r="Q13" s="8">
+      <c r="R13" s="8">
         <v>8</v>
       </c>
-      <c r="R13" s="2">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:18">
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="S13" s="2">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:19">
+      <c r="G14" s="9"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
-      <c r="J14" s="8"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
-      <c r="Q14" s="8"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:18">
-      <c r="F15" s="7"/>
+      <c r="O14" s="8"/>
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:19">
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
-      <c r="J15" s="8"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
       <c r="M15" s="8"/>
       <c r="N15" s="8"/>
-      <c r="Q15" s="8"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:18">
-      <c r="F16" s="7"/>
+      <c r="O15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:19">
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>
-      <c r="J16" s="8"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
       <c r="M16" s="8"/>
       <c r="N16" s="8"/>
-      <c r="Q16" s="8"/>
-    </row>
-    <row r="17" customHeight="1" spans="6:18">
-      <c r="F17" s="7"/>
+      <c r="O16" s="8"/>
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" customHeight="1" spans="7:19">
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
-      <c r="J17" s="8"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
       <c r="M17" s="8"/>
       <c r="N17" s="8"/>
-      <c r="Q17" s="8"/>
-    </row>
-    <row r="18" customHeight="1" spans="6:18">
-      <c r="F18" s="7"/>
+      <c r="O17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" customHeight="1" spans="7:19">
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
-      <c r="J18" s="8"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
       <c r="M18" s="8"/>
       <c r="N18" s="8"/>
-      <c r="Q18" s="8"/>
-    </row>
-    <row r="19" customHeight="1" spans="6:18">
-      <c r="F19" s="7"/>
+      <c r="O18" s="8"/>
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" customHeight="1" spans="7:19">
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
       <c r="M19" s="8"/>
       <c r="N19" s="8"/>
-      <c r="Q19" s="8"/>
-    </row>
-    <row r="20" customHeight="1" spans="6:18">
-      <c r="F20" s="7"/>
+      <c r="O19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" customHeight="1" spans="7:19">
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
-      <c r="J20" s="8"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
       <c r="M20" s="8"/>
       <c r="N20" s="8"/>
-      <c r="Q20" s="8"/>
-    </row>
-    <row r="21" customHeight="1" spans="6:18">
-      <c r="F21" s="7"/>
+      <c r="O20" s="8"/>
+      <c r="R20" s="8"/>
+    </row>
+    <row r="21" customHeight="1" spans="7:19">
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
-      <c r="J21" s="8"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
-      <c r="Q21" s="8"/>
-    </row>
-    <row r="22" customHeight="1" spans="6:18">
-      <c r="F22" s="7"/>
+      <c r="O21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" customHeight="1" spans="7:19">
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="8"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
       <c r="M22" s="8"/>
       <c r="N22" s="8"/>
-      <c r="Q22" s="8"/>
+      <c r="O22" s="8"/>
       <c r="R22" s="8"/>
-    </row>
-    <row r="23" customHeight="1" spans="6:18">
-      <c r="F23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="S22" s="8"/>
+    </row>
+    <row r="23" customHeight="1" spans="7:19">
+      <c r="G23" s="7"/>
       <c r="I23" s="7"/>
-      <c r="J23" s="8"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
-      <c r="Q23" s="8"/>
+      <c r="O23" s="8"/>
       <c r="R23" s="8"/>
-    </row>
-    <row r="24" customHeight="1" spans="6:18">
-      <c r="F24" s="7"/>
+      <c r="S23" s="8"/>
+    </row>
+    <row r="24" customHeight="1" spans="7:19">
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
-      <c r="J24" s="8"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
-      <c r="Q24" s="8"/>
-    </row>
-    <row r="25" customHeight="1" spans="6:18">
-      <c r="F25" s="7"/>
+      <c r="O24" s="8"/>
+      <c r="R24" s="8"/>
+    </row>
+    <row r="25" customHeight="1" spans="7:19">
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
-      <c r="J25" s="8"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
-      <c r="Q25" s="8"/>
-    </row>
-    <row r="26" customHeight="1" spans="6:18">
-      <c r="F26" s="7"/>
+      <c r="O25" s="8"/>
+      <c r="R25" s="8"/>
+    </row>
+    <row r="26" customHeight="1" spans="7:19">
+      <c r="G26" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -89,7 +89,7 @@
     <t>波才</t>
   </si>
   <si>
-    <t>10000</t>
+    <t>50000</t>
   </si>
   <si>
     <t>英灵二层</t>
@@ -98,7 +98,7 @@
     <t>张曼成</t>
   </si>
   <si>
-    <t>40000</t>
+    <t>200000</t>
   </si>
   <si>
     <t>英灵三层</t>
@@ -107,7 +107,7 @@
     <t>程远志</t>
   </si>
   <si>
-    <t>100000</t>
+    <t>600000</t>
   </si>
   <si>
     <t>英灵四层</t>
@@ -116,7 +116,7 @@
     <t>马元义</t>
   </si>
   <si>
-    <t>300000</t>
+    <t>2000000</t>
   </si>
   <si>
     <t>英灵五层</t>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="I6" s="7">
         <f t="shared" ref="I6:I13" si="0">H6*R6*1000</f>
-        <v>10000000</v>
+        <v>50000000</v>
       </c>
       <c r="J6" s="7">
         <v>40</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I7" s="7">
         <f t="shared" si="0"/>
-        <v>80000000</v>
+        <v>400000000</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" ref="J7:J13" si="1">J6+40</f>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
-        <v>300000000</v>
+        <v>1800000000</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="1"/>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>1200000000</v>
+        <v>8000000000</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
@@ -1508,17 +1508,17 @@
         <v>30</v>
       </c>
       <c r="F10" s="1">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G10" s="7">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="H10" s="7">
-        <v>800000</v>
+        <v>4000000</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="0"/>
-        <v>4000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
@@ -1557,17 +1557,17 @@
         <v>32</v>
       </c>
       <c r="F11" s="1">
-        <v>800</v>
+        <v>1100</v>
       </c>
       <c r="G11" s="7">
-        <v>1600000</v>
+        <v>8000000</v>
       </c>
       <c r="H11" s="7">
-        <v>1600000</v>
+        <v>8000000</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="0"/>
-        <v>9600000000</v>
+        <v>48000000000</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
@@ -1606,17 +1606,17 @@
         <v>34</v>
       </c>
       <c r="F12" s="1">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G12" s="7">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="H12" s="7">
-        <v>3000000</v>
+        <v>15000000</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="0"/>
-        <v>21000000000</v>
+        <v>105000000000</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="1"/>
@@ -1655,17 +1655,17 @@
         <v>36</v>
       </c>
       <c r="F13" s="1">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G13" s="7">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="H13" s="7">
-        <v>5000000</v>
+        <v>20000000</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="0"/>
-        <v>40000000000</v>
+        <v>160000000000</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" si="1"/>
@@ -1843,7 +1843,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 F4 F5 C3:E5 G3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
   <si>
     <t>#</t>
   </si>
@@ -83,25 +83,31 @@
     <t>string</t>
   </si>
   <si>
-    <t>英灵一层</t>
+    <t>天级英灵战场</t>
   </si>
   <si>
     <t>波才</t>
   </si>
   <si>
+    <t>20000</t>
+  </si>
+  <si>
     <t>50000</t>
   </si>
   <si>
-    <t>英灵二层</t>
+    <t>地级英灵战场</t>
   </si>
   <si>
     <t>张曼成</t>
   </si>
   <si>
+    <t>100000</t>
+  </si>
+  <si>
     <t>200000</t>
   </si>
   <si>
-    <t>英灵三层</t>
+    <t>玄级英灵战场</t>
   </si>
   <si>
     <t>程远志</t>
@@ -110,7 +116,7 @@
     <t>600000</t>
   </si>
   <si>
-    <t>英灵四层</t>
+    <t>黄级英灵战场</t>
   </si>
   <si>
     <t>马元义</t>
@@ -119,25 +125,25 @@
     <t>2000000</t>
   </si>
   <si>
-    <t>英灵五层</t>
+    <t>宇级英灵战场</t>
   </si>
   <si>
     <t>管亥</t>
   </si>
   <si>
-    <t>英灵六层</t>
+    <t>宙级英灵战场</t>
   </si>
   <si>
     <t>张梁</t>
   </si>
   <si>
-    <t>英灵七层</t>
+    <t>洪级英灵战场</t>
   </si>
   <si>
     <t>张宝</t>
   </si>
   <si>
-    <t>英灵八层</t>
+    <t>荒级英灵战场</t>
   </si>
   <si>
     <t>张角</t>
@@ -1121,7 +1127,7 @@
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.0833333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.75" style="1" customWidth="1"/>
     <col min="5" max="6" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17" style="3" customWidth="1"/>
@@ -1319,7 +1325,7 @@
         <v>19</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" ref="I6:I13" si="0">H6*R6*1000</f>
@@ -1355,19 +1361,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1">
         <v>100</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="0"/>
@@ -1404,19 +1410,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1">
         <v>200</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
@@ -1453,19 +1459,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1">
         <v>400</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
@@ -1502,10 +1508,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1">
         <v>700</v>
@@ -1551,10 +1557,10 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1">
         <v>1100</v>
@@ -1600,10 +1606,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1">
         <v>1500</v>
@@ -1649,10 +1655,10 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" s="1">
         <v>2000</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -1367,7 +1367,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>23</v>
@@ -1416,7 +1416,7 @@
         <v>26</v>
       </c>
       <c r="F8" s="1">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>27</v>
@@ -1465,7 +1465,7 @@
         <v>29</v>
       </c>
       <c r="F9" s="1">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>30</v>
@@ -1514,7 +1514,7 @@
         <v>32</v>
       </c>
       <c r="F10" s="1">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="G10" s="7">
         <v>4000000</v>
@@ -1563,7 +1563,7 @@
         <v>34</v>
       </c>
       <c r="F11" s="1">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="G11" s="7">
         <v>8000000</v>
@@ -1612,7 +1612,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="1">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="G12" s="7">
         <v>15000000</v>
@@ -1661,7 +1661,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="7">
         <v>20000000</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>#</t>
   </si>
@@ -89,7 +89,10 @@
     <t>波才</t>
   </si>
   <si>
-    <t>20000</t>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>40000</t>
   </si>
   <si>
     <t>50000</t>
@@ -101,7 +104,10 @@
     <t>张曼成</t>
   </si>
   <si>
-    <t>100000</t>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>160000</t>
   </si>
   <si>
     <t>200000</t>
@@ -113,6 +119,9 @@
     <t>程远志</t>
   </si>
   <si>
+    <t>480000</t>
+  </si>
+  <si>
     <t>600000</t>
   </si>
   <si>
@@ -120,6 +129,9 @@
   </si>
   <si>
     <t>马元义</t>
+  </si>
+  <si>
+    <t>1600000</t>
   </si>
   <si>
     <t>2000000</t>
@@ -1121,7 +1133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1141,7 +1153,7 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="G1" s="4"/>
@@ -1159,8 +1171,11 @@
       <c r="S1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="G2" s="4"/>
@@ -1178,8 +1193,11 @@
       <c r="S2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:19">
+      <c r="T2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1222,7 +1240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1265,7 +1283,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:19">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
@@ -1308,7 +1326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:19">
+    <row r="6" customHeight="1" spans="1:20">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1329,7 +1347,7 @@
       </c>
       <c r="I6" s="7">
         <f t="shared" ref="I6:I13" si="0">H6*R6*1000</f>
-        <v>50000000</v>
+        <v>40000000</v>
       </c>
       <c r="J6" s="7">
         <v>40</v>
@@ -1355,29 +1373,32 @@
       <c r="S6" s="2">
         <v>1000</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:19">
+      <c r="T6" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:20">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1">
         <v>50</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="0"/>
-        <v>400000000</v>
+        <v>320000000</v>
       </c>
       <c r="J7" s="7">
         <f t="shared" ref="J7:J13" si="1">J6+40</f>
@@ -1404,29 +1425,32 @@
       <c r="S7" s="2">
         <v>2000</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:19">
+      <c r="T7" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:20">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
-        <v>1800000000</v>
+        <v>1440000000</v>
       </c>
       <c r="J8" s="7">
         <f t="shared" si="1"/>
@@ -1453,29 +1477,32 @@
       <c r="S8" s="2">
         <v>4000</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:19">
+      <c r="T8" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:20">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F9" s="1">
         <v>200</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
-        <v>8000000000</v>
+        <v>6400000000</v>
       </c>
       <c r="J9" s="7">
         <f t="shared" si="1"/>
@@ -1502,29 +1529,32 @@
       <c r="S9" s="2">
         <v>8000</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:19">
+      <c r="T9" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:20">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10" s="1">
         <v>300</v>
       </c>
       <c r="G10" s="7">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="H10" s="7">
-        <v>4000000</v>
+        <v>3200000</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" si="0"/>
-        <v>20000000000</v>
+        <v>16000000000</v>
       </c>
       <c r="J10" s="7">
         <f t="shared" si="1"/>
@@ -1551,29 +1581,32 @@
       <c r="S10" s="2">
         <v>16000</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:19">
+      <c r="T10" s="7">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:20">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F11" s="1">
         <v>500</v>
       </c>
       <c r="G11" s="7">
-        <v>8000000</v>
+        <v>6400000</v>
       </c>
       <c r="H11" s="7">
-        <v>8000000</v>
+        <v>6400000</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" si="0"/>
-        <v>48000000000</v>
+        <v>38400000000</v>
       </c>
       <c r="J11" s="7">
         <f t="shared" si="1"/>
@@ -1600,29 +1633,32 @@
       <c r="S11" s="2">
         <v>30000</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:19">
+      <c r="T11" s="7">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:20">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F12" s="1">
         <v>700</v>
       </c>
       <c r="G12" s="7">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="H12" s="7">
-        <v>15000000</v>
+        <v>12000000</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" si="0"/>
-        <v>105000000000</v>
+        <v>84000000000</v>
       </c>
       <c r="J12" s="7">
         <f t="shared" si="1"/>
@@ -1649,29 +1685,32 @@
       <c r="S12" s="2">
         <v>50000</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:19">
+      <c r="T12" s="7">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:20">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F13" s="1">
         <v>1000</v>
       </c>
       <c r="G13" s="7">
-        <v>20000000</v>
+        <v>16000000</v>
       </c>
       <c r="H13" s="7">
-        <v>20000000</v>
+        <v>16000000</v>
       </c>
       <c r="I13" s="7">
         <f t="shared" si="0"/>
-        <v>160000000000</v>
+        <v>128000000000</v>
       </c>
       <c r="J13" s="7">
         <f t="shared" si="1"/>
@@ -1698,8 +1737,11 @@
       <c r="S13" s="2">
         <v>80000</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:19">
+      <c r="T13" s="7">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:20">
       <c r="G14" s="9"/>
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
@@ -1711,7 +1753,7 @@
       <c r="O14" s="8"/>
       <c r="R14" s="8"/>
     </row>
-    <row r="15" customHeight="1" spans="1:19">
+    <row r="15" customHeight="1" spans="1:20">
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
       <c r="I15" s="7"/>
@@ -1723,7 +1765,7 @@
       <c r="O15" s="8"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" customHeight="1" spans="1:19">
+    <row r="16" customHeight="1" spans="1:20">
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
       <c r="I16" s="7"/>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -1700,7 +1700,7 @@
         <v>42</v>
       </c>
       <c r="F13" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="G13" s="7">
         <v>16000000</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,12 +30,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>Id</t>
   </si>
   <si>
     <t>MapName</t>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Protect</t>
-  </si>
-  <si>
-    <t>Id</t>
   </si>
   <si>
     <t>int</t>
@@ -1133,13 +1130,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
     <col min="5" max="6" width="12.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="17" style="3" customWidth="1"/>
@@ -1244,7 +1241,7 @@
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>2</v>
@@ -1287,43 +1284,43 @@
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:20">
@@ -1331,22 +1328,22 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="I6" s="7">
-        <f t="shared" ref="I6:I13" si="0">H6*R6*1000</f>
+        <f t="shared" ref="I6:I14" si="0">H6*R6*1000</f>
         <v>40000000</v>
       </c>
       <c r="J6" s="7">
@@ -1374,7 +1371,7 @@
         <v>1000</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:20">
@@ -1382,19 +1379,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F7" s="1">
         <v>50</v>
       </c>
       <c r="G7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>25</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" si="0"/>
@@ -1426,7 +1423,7 @@
         <v>2000</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:20">
@@ -1434,19 +1431,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" si="0"/>
@@ -1478,7 +1475,7 @@
         <v>4000</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:20">
@@ -1486,19 +1483,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="F9" s="1">
         <v>200</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" si="0"/>
@@ -1530,7 +1527,7 @@
         <v>8000</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:20">
@@ -1538,10 +1535,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F10" s="1">
         <v>300</v>
@@ -1590,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F11" s="1">
         <v>500</v>
@@ -1642,10 +1639,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F12" s="1">
         <v>700</v>
@@ -1694,10 +1691,10 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="F13" s="1">
         <v>900</v>
@@ -1764,6 +1761,8 @@
       <c r="N15" s="8"/>
       <c r="O15" s="8"/>
       <c r="R15" s="8"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="7"/>
     </row>
     <row r="16" customHeight="1" spans="1:20">
       <c r="G16" s="7"/>
@@ -1776,8 +1775,10 @@
       <c r="N16" s="8"/>
       <c r="O16" s="8"/>
       <c r="R16" s="8"/>
-    </row>
-    <row r="17" customHeight="1" spans="7:19">
+      <c r="S16" s="2"/>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" customHeight="1" spans="7:20">
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -1788,8 +1789,10 @@
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="R17" s="8"/>
-    </row>
-    <row r="18" customHeight="1" spans="7:19">
+      <c r="S17" s="2"/>
+      <c r="T17" s="7"/>
+    </row>
+    <row r="18" customHeight="1" spans="7:20">
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
       <c r="I18" s="7"/>
@@ -1800,8 +1803,10 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="R18" s="8"/>
-    </row>
-    <row r="19" customHeight="1" spans="7:19">
+      <c r="S18" s="2"/>
+      <c r="T18" s="7"/>
+    </row>
+    <row r="19" customHeight="1" spans="7:20">
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
       <c r="I19" s="7"/>
@@ -1812,8 +1817,10 @@
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="R19" s="8"/>
-    </row>
-    <row r="20" customHeight="1" spans="7:19">
+      <c r="S19" s="2"/>
+      <c r="T19" s="7"/>
+    </row>
+    <row r="20" customHeight="1" spans="7:20">
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
@@ -1824,8 +1831,10 @@
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
       <c r="R20" s="8"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:19">
+      <c r="S20" s="2"/>
+      <c r="T20" s="7"/>
+    </row>
+    <row r="21" customHeight="1" spans="7:20">
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
       <c r="I21" s="7"/>
@@ -1836,8 +1845,10 @@
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="R21" s="8"/>
-    </row>
-    <row r="22" customHeight="1" spans="7:19">
+      <c r="S21" s="2"/>
+      <c r="T21" s="7"/>
+    </row>
+    <row r="22" customHeight="1" spans="7:20">
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
@@ -1848,10 +1859,12 @@
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
       <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-    </row>
-    <row r="23" customHeight="1" spans="7:19">
+      <c r="S22" s="2"/>
+      <c r="T22" s="7"/>
+    </row>
+    <row r="23" customHeight="1" spans="7:20">
       <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="8"/>
@@ -1860,9 +1873,9 @@
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
       <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-    </row>
-    <row r="24" customHeight="1" spans="7:19">
+      <c r="T23" s="7"/>
+    </row>
+    <row r="24" customHeight="1" spans="7:20">
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
@@ -1873,8 +1886,9 @@
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
       <c r="R24" s="8"/>
-    </row>
-    <row r="25" customHeight="1" spans="7:19">
+      <c r="T24" s="7"/>
+    </row>
+    <row r="25" customHeight="1" spans="7:20">
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
@@ -1885,13 +1899,76 @@
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
       <c r="R25" s="8"/>
-    </row>
-    <row r="26" customHeight="1" spans="7:19">
+      <c r="T25" s="7"/>
+    </row>
+    <row r="26" customHeight="1" spans="7:20">
       <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="T26" s="7"/>
+    </row>
+    <row r="27" customHeight="1" spans="7:20">
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="T27" s="7"/>
+    </row>
+    <row r="28" customHeight="1" spans="7:20">
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="T28" s="7"/>
+    </row>
+    <row r="29" customHeight="1" spans="7:20">
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="T29" s="7"/>
+    </row>
+    <row r="30" customHeight="1" spans="7:20">
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="T30" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3:O3 C4:O5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Id</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>MapName</t>
   </si>
   <si>
@@ -156,6 +159,60 @@
   </si>
   <si>
     <t>张角</t>
+  </si>
+  <si>
+    <t>吴国·天级战场</t>
+  </si>
+  <si>
+    <t>马谡</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>吴国·地级战场</t>
+  </si>
+  <si>
+    <t>张苞</t>
+  </si>
+  <si>
+    <t>吴国·玄级战场</t>
+  </si>
+  <si>
+    <t>徐庶</t>
+  </si>
+  <si>
+    <t>吴国·黄级战场</t>
+  </si>
+  <si>
+    <t>姜维</t>
+  </si>
+  <si>
+    <t>6000000</t>
+  </si>
+  <si>
+    <t>吴国·宇级战场</t>
+  </si>
+  <si>
+    <t>马云禄</t>
+  </si>
+  <si>
+    <t>吴国·宙级战场</t>
+  </si>
+  <si>
+    <t>魏延</t>
+  </si>
+  <si>
+    <t>吴国·洪级战场</t>
+  </si>
+  <si>
+    <t>张飞</t>
+  </si>
+  <si>
+    <t>吴国·荒级战场</t>
+  </si>
+  <si>
+    <t>刘备</t>
   </si>
 </sst>
 </file>
@@ -169,7 +226,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,6 +236,12 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -657,137 +720,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -805,9 +868,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1130,71 +1192,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="8" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="3" customWidth="1"/>
-    <col min="10" max="10" width="13.1666666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.83333333333333" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="8" style="2" customWidth="1"/>
-    <col min="14" max="14" width="7.08333333333333" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.5" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="1" customWidth="1"/>
+    <col min="6" max="7" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="17" style="3" customWidth="1"/>
+    <col min="10" max="10" width="19.25" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.1666666666667" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.83333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="8" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.08333333333333" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.5" style="2" customWidth="1"/>
+    <col min="17" max="20" width="9" style="2"/>
+    <col min="21" max="21" width="10" style="2"/>
+    <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="2"/>
+      <c r="K1" s="4"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="R1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="P1" s="2"/>
       <c r="S1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
-      <c r="K2" s="2"/>
+      <c r="K2" s="4"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
-      <c r="R2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="P2" s="2"/>
       <c r="S2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="U2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="s">
@@ -1209,7 +1273,7 @@
       <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -1221,7 +1285,7 @@
       <c r="J3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="5" t="s">
@@ -1236,8 +1300,11 @@
       <c r="O3" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="P3" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="5" t="s">
@@ -1252,7 +1319,7 @@
       <c r="F4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="6" t="s">
@@ -1264,7 +1331,7 @@
       <c r="J4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="L4" s="5" t="s">
@@ -1279,82 +1346,88 @@
       <c r="O4" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:20">
+      <c r="P4" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:21">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="N5" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:20">
+        <v>15</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:21">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
+      <c r="D6" s="1">
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="7">
-        <f t="shared" ref="I6:I14" si="0">H6*R6*1000</f>
+      <c r="I6" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" ref="J6:J14" si="0">I6*S6*1000</f>
         <v>40000000</v>
       </c>
-      <c r="J6" s="7">
+      <c r="K6" s="7">
         <v>40</v>
       </c>
-      <c r="K6" s="8">
+      <c r="L6" s="8">
         <v>100</v>
       </c>
-      <c r="L6" s="8">
-        <v>1800</v>
-      </c>
       <c r="M6" s="8">
         <v>1800</v>
       </c>
@@ -1362,51 +1435,54 @@
         <v>1800</v>
       </c>
       <c r="O6" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P6" s="8">
         <v>99</v>
       </c>
-      <c r="R6" s="8">
+      <c r="S6" s="8">
         <v>1</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>1000</v>
       </c>
-      <c r="T6" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:20">
+      <c r="U6" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:21">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
+      <c r="D7" s="1">
+        <v>1</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
         <v>50</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>320000000</v>
       </c>
-      <c r="J7" s="7">
-        <f t="shared" ref="J7:J13" si="1">J6+40</f>
+      <c r="K7" s="7">
+        <f t="shared" ref="K7:K13" si="1">K6+40</f>
         <v>80</v>
       </c>
-      <c r="K7" s="8">
+      <c r="L7" s="8">
         <v>100</v>
       </c>
-      <c r="L7" s="8">
-        <v>1800</v>
-      </c>
       <c r="M7" s="8">
         <v>1800</v>
       </c>
@@ -1414,51 +1490,54 @@
         <v>1800</v>
       </c>
       <c r="O7" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P7" s="8">
         <v>99</v>
       </c>
-      <c r="R7" s="8">
+      <c r="S7" s="8">
         <v>2</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>2000</v>
       </c>
-      <c r="T7" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:20">
+      <c r="U7" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:21">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
+      <c r="D8" s="1">
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1">
         <v>100</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="7">
+      <c r="H8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="7">
         <f t="shared" si="0"/>
         <v>1440000000</v>
       </c>
-      <c r="J8" s="7">
+      <c r="K8" s="7">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
-      <c r="K8" s="8">
+      <c r="L8" s="8">
         <v>100</v>
       </c>
-      <c r="L8" s="8">
-        <v>1800</v>
-      </c>
       <c r="M8" s="8">
         <v>1800</v>
       </c>
@@ -1466,51 +1545,54 @@
         <v>1800</v>
       </c>
       <c r="O8" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P8" s="8">
         <v>99</v>
       </c>
-      <c r="R8" s="8">
+      <c r="S8" s="8">
         <v>3</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>4000</v>
       </c>
-      <c r="T8" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:20">
+      <c r="U8" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:21">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
+      <c r="D9" s="1">
+        <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1">
         <v>200</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="7">
+      <c r="H9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="7">
         <f t="shared" si="0"/>
         <v>6400000000</v>
       </c>
-      <c r="J9" s="7">
+      <c r="K9" s="7">
         <f t="shared" si="1"/>
         <v>160</v>
       </c>
-      <c r="K9" s="8">
+      <c r="L9" s="8">
         <v>100</v>
       </c>
-      <c r="L9" s="8">
-        <v>1800</v>
-      </c>
       <c r="M9" s="8">
         <v>1800</v>
       </c>
@@ -1518,51 +1600,54 @@
         <v>1800</v>
       </c>
       <c r="O9" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P9" s="8">
         <v>99</v>
       </c>
-      <c r="R9" s="8">
+      <c r="S9" s="8">
         <v>4</v>
       </c>
-      <c r="S9" s="2">
+      <c r="T9" s="2">
         <v>8000</v>
       </c>
-      <c r="T9" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:20">
+      <c r="U9" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:21">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
+      <c r="D10" s="1">
+        <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="1">
         <v>300</v>
-      </c>
-      <c r="G10" s="7">
-        <v>3200000</v>
       </c>
       <c r="H10" s="7">
         <v>3200000</v>
       </c>
       <c r="I10" s="7">
+        <v>3200000</v>
+      </c>
+      <c r="J10" s="7">
         <f t="shared" si="0"/>
         <v>16000000000</v>
       </c>
-      <c r="J10" s="7">
+      <c r="K10" s="7">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="K10" s="8">
+      <c r="L10" s="8">
         <v>100</v>
       </c>
-      <c r="L10" s="8">
-        <v>1800</v>
-      </c>
       <c r="M10" s="8">
         <v>1800</v>
       </c>
@@ -1570,51 +1655,54 @@
         <v>1800</v>
       </c>
       <c r="O10" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P10" s="8">
         <v>99</v>
       </c>
-      <c r="R10" s="8">
+      <c r="S10" s="8">
         <v>5</v>
       </c>
-      <c r="S10" s="2">
+      <c r="T10" s="2">
         <v>16000</v>
       </c>
-      <c r="T10" s="7">
+      <c r="U10" s="7">
         <v>4000000</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:20">
+    <row r="11" ht="18" customHeight="1" spans="1:21">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>36</v>
+      <c r="D11" s="1">
+        <v>1</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="1">
         <v>500</v>
-      </c>
-      <c r="G11" s="7">
-        <v>6400000</v>
       </c>
       <c r="H11" s="7">
         <v>6400000</v>
       </c>
       <c r="I11" s="7">
+        <v>6400000</v>
+      </c>
+      <c r="J11" s="7">
         <f t="shared" si="0"/>
         <v>38400000000</v>
       </c>
-      <c r="J11" s="7">
+      <c r="K11" s="7">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K11" s="8">
+      <c r="L11" s="8">
         <v>100</v>
       </c>
-      <c r="L11" s="8">
-        <v>1800</v>
-      </c>
       <c r="M11" s="8">
         <v>1800</v>
       </c>
@@ -1622,51 +1710,54 @@
         <v>1800</v>
       </c>
       <c r="O11" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P11" s="8">
         <v>99</v>
       </c>
-      <c r="R11" s="8">
+      <c r="S11" s="8">
         <v>6</v>
       </c>
-      <c r="S11" s="2">
+      <c r="T11" s="2">
         <v>30000</v>
       </c>
-      <c r="T11" s="7">
+      <c r="U11" s="7">
         <v>8000000</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:20">
+    <row r="12" ht="18" customHeight="1" spans="1:21">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
+      <c r="D12" s="1">
+        <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1">
         <v>700</v>
-      </c>
-      <c r="G12" s="7">
-        <v>12000000</v>
       </c>
       <c r="H12" s="7">
         <v>12000000</v>
       </c>
       <c r="I12" s="7">
+        <v>12000000</v>
+      </c>
+      <c r="J12" s="7">
         <f t="shared" si="0"/>
         <v>84000000000</v>
       </c>
-      <c r="J12" s="7">
+      <c r="K12" s="7">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="K12" s="8">
+      <c r="L12" s="8">
         <v>100</v>
       </c>
-      <c r="L12" s="8">
-        <v>1800</v>
-      </c>
       <c r="M12" s="8">
         <v>1800</v>
       </c>
@@ -1674,51 +1765,54 @@
         <v>1800</v>
       </c>
       <c r="O12" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P12" s="8">
         <v>99</v>
       </c>
-      <c r="R12" s="8">
+      <c r="S12" s="8">
         <v>7</v>
       </c>
-      <c r="S12" s="2">
+      <c r="T12" s="2">
         <v>50000</v>
       </c>
-      <c r="T12" s="7">
+      <c r="U12" s="7">
         <v>15000000</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:20">
+    <row r="13" ht="18" customHeight="1" spans="1:21">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>40</v>
+      <c r="D13" s="1">
+        <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="1">
         <v>900</v>
-      </c>
-      <c r="G13" s="7">
-        <v>16000000</v>
       </c>
       <c r="H13" s="7">
         <v>16000000</v>
       </c>
       <c r="I13" s="7">
+        <v>16000000</v>
+      </c>
+      <c r="J13" s="7">
         <f t="shared" si="0"/>
         <v>128000000000</v>
       </c>
-      <c r="J13" s="7">
+      <c r="K13" s="7">
         <f t="shared" si="1"/>
         <v>320</v>
       </c>
-      <c r="K13" s="8">
+      <c r="L13" s="8">
         <v>100</v>
       </c>
-      <c r="L13" s="8">
-        <v>1800</v>
-      </c>
       <c r="M13" s="8">
         <v>1800</v>
       </c>
@@ -1726,254 +1820,577 @@
         <v>1800</v>
       </c>
       <c r="O13" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P13" s="8">
         <v>99</v>
       </c>
-      <c r="R13" s="8">
+      <c r="S13" s="8">
         <v>8</v>
       </c>
-      <c r="S13" s="2">
+      <c r="T13" s="2">
         <v>80000</v>
       </c>
-      <c r="T13" s="7">
+      <c r="U13" s="7">
         <v>20000000</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="1:20">
-      <c r="G14" s="9"/>
+    <row r="14" ht="18" customHeight="1" spans="1:21">
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
-      <c r="K14" s="8"/>
+      <c r="K14" s="7"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
       <c r="O14" s="8"/>
-      <c r="R14" s="8"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:20">
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:20">
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="7"/>
-    </row>
-    <row r="17" customHeight="1" spans="7:20">
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="7:20">
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="7:20">
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="7:20">
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="7:20">
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="7"/>
-    </row>
-    <row r="22" customHeight="1" spans="7:20">
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="7"/>
-    </row>
-    <row r="23" customHeight="1" spans="7:20">
-      <c r="G23" s="7"/>
+      <c r="P14" s="8"/>
+      <c r="S14" s="8"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:21">
+      <c r="C15" s="1">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="1">
+        <v>300</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J15" s="7">
+        <f t="shared" ref="J15:J22" si="2">I15*S15*1000</f>
+        <v>450000000</v>
+      </c>
+      <c r="K15" s="7">
+        <v>80</v>
+      </c>
+      <c r="L15" s="8">
+        <v>100</v>
+      </c>
+      <c r="M15" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N15" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O15" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P15" s="8">
+        <v>99</v>
+      </c>
+      <c r="S15" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="T15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="U15" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:21">
+      <c r="C16" s="1">
+        <v>10</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="1">
+        <v>500</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J16" s="7">
+        <f t="shared" si="2"/>
+        <v>1800000000</v>
+      </c>
+      <c r="K16" s="7">
+        <v>120</v>
+      </c>
+      <c r="L16" s="8">
+        <v>100</v>
+      </c>
+      <c r="M16" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N16" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O16" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P16" s="8">
+        <v>99</v>
+      </c>
+      <c r="S16" s="8">
+        <v>3</v>
+      </c>
+      <c r="T16" s="2">
+        <v>2000</v>
+      </c>
+      <c r="U16" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="3:21">
+      <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="1">
+        <v>700</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="7">
+        <f t="shared" si="2"/>
+        <v>900000000</v>
+      </c>
+      <c r="K17" s="7">
+        <v>160</v>
+      </c>
+      <c r="L17" s="8">
+        <v>100</v>
+      </c>
+      <c r="M17" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N17" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O17" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P17" s="8">
+        <v>99</v>
+      </c>
+      <c r="S17" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="T17" s="2">
+        <v>4000</v>
+      </c>
+      <c r="U17" s="11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="3:21">
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="1">
+        <v>900</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="2"/>
+        <v>36000000000</v>
+      </c>
+      <c r="K18" s="7">
+        <v>200</v>
+      </c>
+      <c r="L18" s="8">
+        <v>100</v>
+      </c>
+      <c r="M18" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N18" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O18" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P18" s="8">
+        <v>99</v>
+      </c>
+      <c r="S18" s="8">
+        <v>6</v>
+      </c>
+      <c r="T18" s="2">
+        <v>8000</v>
+      </c>
+      <c r="U18" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="3:21">
+      <c r="C19" s="1">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1200000</v>
+      </c>
+      <c r="I19" s="7">
+        <v>12000000</v>
+      </c>
+      <c r="J19" s="7">
+        <f t="shared" si="2"/>
+        <v>96000000000</v>
+      </c>
+      <c r="K19" s="7">
+        <v>240</v>
+      </c>
+      <c r="L19" s="8">
+        <v>100</v>
+      </c>
+      <c r="M19" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N19" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O19" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P19" s="8">
+        <v>99</v>
+      </c>
+      <c r="S19" s="8">
+        <v>8</v>
+      </c>
+      <c r="T19" s="2">
+        <v>16000</v>
+      </c>
+      <c r="U19" s="7">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="3:21">
+      <c r="C20" s="1">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2400000</v>
+      </c>
+      <c r="I20" s="7">
+        <v>25000000</v>
+      </c>
+      <c r="J20" s="7">
+        <f t="shared" si="2"/>
+        <v>250000000000</v>
+      </c>
+      <c r="K20" s="7">
+        <v>280</v>
+      </c>
+      <c r="L20" s="8">
+        <v>100</v>
+      </c>
+      <c r="M20" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N20" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O20" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P20" s="8">
+        <v>99</v>
+      </c>
+      <c r="S20" s="8">
+        <v>10</v>
+      </c>
+      <c r="T20" s="2">
+        <v>30000</v>
+      </c>
+      <c r="U20" s="7">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="3:21">
+      <c r="C21" s="1">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>40000000</v>
+      </c>
+      <c r="I21" s="7">
+        <v>50000000</v>
+      </c>
+      <c r="J21" s="7">
+        <f t="shared" si="2"/>
+        <v>600000000000</v>
+      </c>
+      <c r="K21" s="7">
+        <v>320</v>
+      </c>
+      <c r="L21" s="8">
+        <v>100</v>
+      </c>
+      <c r="M21" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N21" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O21" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P21" s="8">
+        <v>99</v>
+      </c>
+      <c r="S21" s="8">
+        <v>12</v>
+      </c>
+      <c r="T21" s="2">
+        <v>50000</v>
+      </c>
+      <c r="U21" s="7">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="3:21">
+      <c r="C22" s="1">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2400</v>
+      </c>
+      <c r="H22" s="7">
+        <v>60000000</v>
+      </c>
+      <c r="I22" s="7">
+        <v>80000000</v>
+      </c>
+      <c r="J22" s="7">
+        <f t="shared" si="2"/>
+        <v>1200000000000</v>
+      </c>
+      <c r="K22" s="7">
+        <v>360</v>
+      </c>
+      <c r="L22" s="8">
+        <v>100</v>
+      </c>
+      <c r="M22" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N22" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O22" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P22" s="8">
+        <v>99</v>
+      </c>
+      <c r="S22" s="8">
+        <v>15</v>
+      </c>
+      <c r="T22" s="2">
+        <v>80000</v>
+      </c>
+      <c r="U22" s="7">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:21">
       <c r="H23" s="7"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
-      <c r="K23" s="8"/>
+      <c r="K23" s="7"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
       <c r="N23" s="8"/>
       <c r="O23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="T23" s="7"/>
-    </row>
-    <row r="24" customHeight="1" spans="7:20">
-      <c r="G24" s="7"/>
+      <c r="P23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="U23" s="7"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:21">
       <c r="H24" s="7"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
-      <c r="K24" s="8"/>
+      <c r="K24" s="7"/>
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="T24" s="7"/>
-    </row>
-    <row r="25" customHeight="1" spans="7:20">
-      <c r="G25" s="7"/>
+      <c r="P24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="U24" s="7"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:21">
       <c r="H25" s="7"/>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
-      <c r="K25" s="8"/>
+      <c r="K25" s="7"/>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="8"/>
       <c r="O25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="T25" s="7"/>
-    </row>
-    <row r="26" customHeight="1" spans="7:20">
-      <c r="G26" s="7"/>
+      <c r="P25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="U25" s="7"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:21">
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
-      <c r="K26" s="8"/>
+      <c r="K26" s="7"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="T26" s="7"/>
-    </row>
-    <row r="27" customHeight="1" spans="7:20">
-      <c r="G27" s="7"/>
+      <c r="P26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="U26" s="7"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:21">
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
       <c r="J27" s="7"/>
-      <c r="K27" s="8"/>
+      <c r="K27" s="7"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="T27" s="7"/>
-    </row>
-    <row r="28" customHeight="1" spans="7:20">
-      <c r="G28" s="7"/>
+      <c r="P27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="U27" s="7"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:21">
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
-      <c r="K28" s="8"/>
+      <c r="K28" s="7"/>
       <c r="L28" s="8"/>
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="T28" s="7"/>
-    </row>
-    <row r="29" customHeight="1" spans="7:20">
-      <c r="G29" s="7"/>
+      <c r="P28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="U28" s="7"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:21">
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7"/>
-      <c r="K29" s="8"/>
+      <c r="K29" s="7"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="T29" s="7"/>
-    </row>
-    <row r="30" customHeight="1" spans="7:20">
-      <c r="G30" s="7"/>
+      <c r="P29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="U29" s="7"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:21">
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
-      <c r="K30" s="8"/>
+      <c r="K30" s="7"/>
       <c r="L30" s="8"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
       <c r="O30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="T30" s="7"/>
+      <c r="P30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="U30" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3:O3 C4:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:P5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="E9" r:id="rId1" display="马元义" tooltip="https://baike.baidu.com/item/%E9%A9%AC%E5%85%83%E4%B9%89/2282194?fromModule=lemma_inlink"/>
+    <hyperlink ref="F9" r:id="rId1" display="马元义" tooltip="https://baike.baidu.com/item/%E9%A9%AC%E5%85%83%E4%B9%89/2282194?fromModule=lemma_inlink"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>#</t>
   </si>
@@ -167,7 +167,7 @@
     <t>马谡</t>
   </si>
   <si>
-    <t>300000</t>
+    <t>240000</t>
   </si>
   <si>
     <t>吴国·地级战场</t>
@@ -182,13 +182,16 @@
     <t>徐庶</t>
   </si>
   <si>
+    <t>1240000</t>
+  </si>
+  <si>
     <t>吴国·黄级战场</t>
   </si>
   <si>
     <t>姜维</t>
   </si>
   <si>
-    <t>6000000</t>
+    <t>4000000</t>
   </si>
   <si>
     <t>吴国·宇级战场</t>
@@ -1871,7 +1874,7 @@
       </c>
       <c r="J15" s="7">
         <f t="shared" ref="J15:J22" si="2">I15*S15*1000</f>
-        <v>450000000</v>
+        <v>360000000</v>
       </c>
       <c r="K15" s="7">
         <v>80</v>
@@ -1918,14 +1921,14 @@
         <v>500</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="7">
         <f t="shared" si="2"/>
-        <v>1800000000</v>
+        <v>1440000000</v>
       </c>
       <c r="K16" s="7">
         <v>120</v>
@@ -1972,14 +1975,14 @@
         <v>700</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="J17" s="7">
         <f t="shared" si="2"/>
-        <v>900000000</v>
+        <v>5580000000</v>
       </c>
       <c r="K17" s="7">
         <v>160</v>
@@ -2017,23 +2020,23 @@
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="1">
         <v>900</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18" s="7">
         <f t="shared" si="2"/>
-        <v>36000000000</v>
+        <v>24000000000</v>
       </c>
       <c r="K18" s="7">
         <v>200</v>
@@ -2071,23 +2074,23 @@
         <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="1">
         <v>1200</v>
       </c>
       <c r="H19" s="7">
-        <v>1200000</v>
+        <v>1000000</v>
       </c>
       <c r="I19" s="7">
-        <v>12000000</v>
+        <v>1000000</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="2"/>
-        <v>96000000000</v>
+        <v>8000000000</v>
       </c>
       <c r="K19" s="7">
         <v>240</v>
@@ -2125,23 +2128,23 @@
         <v>2</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" s="1">
         <v>1600</v>
       </c>
       <c r="H20" s="7">
-        <v>2400000</v>
+        <v>2000000</v>
       </c>
       <c r="I20" s="7">
-        <v>25000000</v>
+        <v>2000000</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="2"/>
-        <v>250000000000</v>
+        <v>20000000000</v>
       </c>
       <c r="K20" s="7">
         <v>280</v>
@@ -2179,23 +2182,23 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G21" s="1">
         <v>2000</v>
       </c>
       <c r="H21" s="7">
+        <v>32000000</v>
+      </c>
+      <c r="I21" s="7">
         <v>40000000</v>
-      </c>
-      <c r="I21" s="7">
-        <v>50000000</v>
       </c>
       <c r="J21" s="7">
         <f t="shared" si="2"/>
-        <v>600000000000</v>
+        <v>480000000000</v>
       </c>
       <c r="K21" s="7">
         <v>320</v>
@@ -2233,23 +2236,23 @@
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G22" s="1">
         <v>2400</v>
       </c>
       <c r="H22" s="7">
-        <v>60000000</v>
+        <v>50000000</v>
       </c>
       <c r="I22" s="7">
-        <v>80000000</v>
+        <v>64000000</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="2"/>
-        <v>1200000000000</v>
+        <v>960000000000</v>
       </c>
       <c r="K22" s="7">
         <v>360</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -2083,14 +2083,14 @@
         <v>1200</v>
       </c>
       <c r="H19" s="7">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="I19" s="7">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="J19" s="7">
         <f t="shared" si="2"/>
-        <v>8000000000</v>
+        <v>80000000000</v>
       </c>
       <c r="K19" s="7">
         <v>240</v>
@@ -2137,14 +2137,14 @@
         <v>1600</v>
       </c>
       <c r="H20" s="7">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="I20" s="7">
-        <v>2000000</v>
+        <v>20000000</v>
       </c>
       <c r="J20" s="7">
         <f t="shared" si="2"/>
-        <v>20000000000</v>
+        <v>200000000000</v>
       </c>
       <c r="K20" s="7">
         <v>280</v>
@@ -2248,11 +2248,11 @@
         <v>50000000</v>
       </c>
       <c r="I22" s="7">
-        <v>64000000</v>
+        <v>80000000</v>
       </c>
       <c r="J22" s="7">
         <f t="shared" si="2"/>
-        <v>960000000000</v>
+        <v>1200000000000</v>
       </c>
       <c r="K22" s="7">
         <v>360</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -1864,7 +1864,7 @@
         <v>44</v>
       </c>
       <c r="G15" s="1">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>45</v>
@@ -1918,7 +1918,7 @@
         <v>47</v>
       </c>
       <c r="G16" s="1">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>29</v>

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
   <si>
     <t>#</t>
   </si>
@@ -216,6 +216,95 @@
   </si>
   <si>
     <t>刘备</t>
+  </si>
+  <si>
+    <t>魏国·天级战场</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蒋钦</t>
+    </r>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
+    <t>1200000</t>
+  </si>
+  <si>
+    <t>魏国·地级战场</t>
+  </si>
+  <si>
+    <t>丁奉</t>
+  </si>
+  <si>
+    <t>1800000</t>
+  </si>
+  <si>
+    <t>2400000</t>
+  </si>
+  <si>
+    <t>魏国·玄级战场</t>
+  </si>
+  <si>
+    <t>陆抗</t>
+  </si>
+  <si>
+    <t>4800000</t>
+  </si>
+  <si>
+    <t>6000000</t>
+  </si>
+  <si>
+    <t>魏国·黄级战场</t>
+  </si>
+  <si>
+    <t>吕蒙</t>
+  </si>
+  <si>
+    <t>16000000</t>
+  </si>
+  <si>
+    <t>20000000</t>
+  </si>
+  <si>
+    <t>魏国·宇级战场</t>
+  </si>
+  <si>
+    <t>步练师</t>
+  </si>
+  <si>
+    <t>魏国·宙级战场</t>
+  </si>
+  <si>
+    <t>大乔</t>
+  </si>
+  <si>
+    <t>魏国·洪级战场</t>
+  </si>
+  <si>
+    <t>陆逊</t>
+  </si>
+  <si>
+    <t>魏国·荒级战场</t>
+  </si>
+  <si>
+    <t>孙权</t>
   </si>
 </sst>
 </file>
@@ -229,7 +318,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,6 +340,30 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -723,137 +836,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -873,6 +986,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1195,7 +1314,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1415,10 +1534,10 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="7">
@@ -1449,7 +1568,7 @@
       <c r="T6" s="2">
         <v>1000</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="U6" s="15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1469,10 +1588,10 @@
       <c r="G7" s="1">
         <v>50</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="15" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="7">
@@ -1504,7 +1623,7 @@
       <c r="T7" s="2">
         <v>2000</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1524,10 +1643,10 @@
       <c r="G8" s="1">
         <v>100</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="J8" s="7">
@@ -1559,7 +1678,7 @@
       <c r="T8" s="2">
         <v>4000</v>
       </c>
-      <c r="U8" s="11" t="s">
+      <c r="U8" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1579,10 +1698,10 @@
       <c r="G9" s="1">
         <v>200</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="15" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="7">
@@ -1614,7 +1733,7 @@
       <c r="T9" s="2">
         <v>8000</v>
       </c>
-      <c r="U9" s="11" t="s">
+      <c r="U9" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1866,10 +1985,10 @@
       <c r="G15" s="1">
         <v>200</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="15" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="7">
@@ -1900,7 +2019,7 @@
       <c r="T15" s="2">
         <v>1000</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="U15" s="15" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1920,10 +2039,10 @@
       <c r="G16" s="1">
         <v>450</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="15" t="s">
         <v>29</v>
       </c>
       <c r="J16" s="7">
@@ -1954,7 +2073,7 @@
       <c r="T16" s="2">
         <v>2000</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="U16" s="15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1974,10 +2093,10 @@
       <c r="G17" s="1">
         <v>700</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="15" t="s">
         <v>50</v>
       </c>
       <c r="J17" s="7">
@@ -2008,7 +2127,7 @@
       <c r="T17" s="2">
         <v>4000</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="U17" s="15" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2028,10 +2147,10 @@
       <c r="G18" s="1">
         <v>900</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="15" t="s">
         <v>53</v>
       </c>
       <c r="J18" s="7">
@@ -2062,7 +2181,7 @@
       <c r="T18" s="2">
         <v>8000</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="U18" s="15" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2296,95 +2415,477 @@
       <c r="U23" s="7"/>
     </row>
     <row r="24" customHeight="1" spans="3:21">
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="U24" s="7"/>
+      <c r="C24" s="1">
+        <v>17</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="1">
+        <v>900</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="7">
+        <f t="shared" ref="J24:J31" si="3">I24*S24*1200</f>
+        <v>2880000000</v>
+      </c>
+      <c r="K24" s="7">
+        <v>120</v>
+      </c>
+      <c r="L24" s="8">
+        <v>100</v>
+      </c>
+      <c r="M24" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N24" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O24" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P24" s="8">
+        <v>99</v>
+      </c>
+      <c r="S24" s="8">
+        <v>2</v>
+      </c>
+      <c r="T24" s="2">
+        <v>1000</v>
+      </c>
+      <c r="U24" s="15" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="25" customHeight="1" spans="3:21">
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="U25" s="7"/>
+      <c r="C25" s="1">
+        <v>18</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="J25" s="7">
+        <f t="shared" si="3"/>
+        <v>11520000000</v>
+      </c>
+      <c r="K25" s="7">
+        <v>160</v>
+      </c>
+      <c r="L25" s="8">
+        <v>100</v>
+      </c>
+      <c r="M25" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N25" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O25" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P25" s="8">
+        <v>99</v>
+      </c>
+      <c r="S25" s="8">
+        <v>4</v>
+      </c>
+      <c r="T25" s="2">
+        <v>2000</v>
+      </c>
+      <c r="U25" s="15" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="26" customHeight="1" spans="3:21">
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="U26" s="7"/>
+      <c r="C26" s="1">
+        <v>19</v>
+      </c>
+      <c r="D26" s="1">
+        <v>3</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1600</v>
+      </c>
+      <c r="H26" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="I26" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="J26" s="7">
+        <f t="shared" si="3"/>
+        <v>43200000000</v>
+      </c>
+      <c r="K26" s="7">
+        <v>200</v>
+      </c>
+      <c r="L26" s="8">
+        <v>100</v>
+      </c>
+      <c r="M26" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N26" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O26" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P26" s="8">
+        <v>99</v>
+      </c>
+      <c r="S26" s="8">
+        <v>6</v>
+      </c>
+      <c r="T26" s="2">
+        <v>4000</v>
+      </c>
+      <c r="U26" s="15" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="27" customHeight="1" spans="3:21">
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="U27" s="7"/>
+      <c r="C27" s="1">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J27" s="7">
+        <f t="shared" si="3"/>
+        <v>192000000000</v>
+      </c>
+      <c r="K27" s="7">
+        <v>240</v>
+      </c>
+      <c r="L27" s="8">
+        <v>100</v>
+      </c>
+      <c r="M27" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N27" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O27" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P27" s="8">
+        <v>99</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="2">
+        <v>8000</v>
+      </c>
+      <c r="U27" s="15" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="28" customHeight="1" spans="3:21">
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="U28" s="7"/>
+      <c r="C28" s="1">
+        <v>21</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="G28" s="1">
+        <v>2400</v>
+      </c>
+      <c r="H28" s="7">
+        <v>40000000</v>
+      </c>
+      <c r="I28" s="7">
+        <v>50000000</v>
+      </c>
+      <c r="J28" s="7">
+        <f t="shared" si="3"/>
+        <v>600000000000</v>
+      </c>
+      <c r="K28" s="7">
+        <v>280</v>
+      </c>
+      <c r="L28" s="8">
+        <v>100</v>
+      </c>
+      <c r="M28" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N28" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O28" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P28" s="8">
+        <v>99</v>
+      </c>
+      <c r="S28" s="8">
+        <v>10</v>
+      </c>
+      <c r="T28" s="2">
+        <v>16000</v>
+      </c>
+      <c r="U28" s="7">
+        <v>4000000</v>
+      </c>
     </row>
     <row r="29" customHeight="1" spans="3:21">
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="U29" s="7"/>
+      <c r="C29" s="1">
+        <v>22</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2900</v>
+      </c>
+      <c r="H29" s="7">
+        <v>80000000</v>
+      </c>
+      <c r="I29" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="J29" s="7">
+        <f t="shared" si="3"/>
+        <v>1440000000000</v>
+      </c>
+      <c r="K29" s="7">
+        <v>320</v>
+      </c>
+      <c r="L29" s="8">
+        <v>100</v>
+      </c>
+      <c r="M29" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N29" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O29" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P29" s="8">
+        <v>99</v>
+      </c>
+      <c r="S29" s="8">
+        <v>12</v>
+      </c>
+      <c r="T29" s="2">
+        <v>30000</v>
+      </c>
+      <c r="U29" s="7">
+        <v>8000000</v>
+      </c>
     </row>
     <row r="30" customHeight="1" spans="3:21">
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="U30" s="7"/>
+      <c r="C30" s="1">
+        <v>23</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="1">
+        <v>3400</v>
+      </c>
+      <c r="H30" s="7">
+        <v>160000000</v>
+      </c>
+      <c r="I30" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="J30" s="7">
+        <f t="shared" si="3"/>
+        <v>3600000000000</v>
+      </c>
+      <c r="K30" s="7">
+        <v>360</v>
+      </c>
+      <c r="L30" s="8">
+        <v>100</v>
+      </c>
+      <c r="M30" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N30" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O30" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P30" s="8">
+        <v>99</v>
+      </c>
+      <c r="S30" s="8">
+        <v>15</v>
+      </c>
+      <c r="T30" s="2">
+        <v>50000</v>
+      </c>
+      <c r="U30" s="7">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:21">
+      <c r="C31" s="1">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>320000000</v>
+      </c>
+      <c r="I31" s="7">
+        <v>400000000</v>
+      </c>
+      <c r="J31" s="7">
+        <f t="shared" si="3"/>
+        <v>8640000000000</v>
+      </c>
+      <c r="K31" s="7">
+        <v>400</v>
+      </c>
+      <c r="L31" s="8">
+        <v>100</v>
+      </c>
+      <c r="M31" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N31" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O31" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P31" s="8">
+        <v>99</v>
+      </c>
+      <c r="S31" s="8">
+        <v>18</v>
+      </c>
+      <c r="T31" s="2">
+        <v>80000</v>
+      </c>
+      <c r="U31" s="7">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:21">
+      <c r="I32" s="7"/>
+    </row>
+    <row r="36" customHeight="1" spans="8:9">
+      <c r="I36" s="7"/>
+    </row>
+    <row r="37" customHeight="1" spans="8:9">
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" customHeight="1" spans="8:9">
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" customHeight="1" spans="8:9">
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" customHeight="1" spans="8:9">
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" customHeight="1" spans="8:9">
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+    </row>
+    <row r="42" customHeight="1" spans="8:9">
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" customHeight="1" spans="8:9">
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" customHeight="1" spans="8:9">
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" customHeight="1" spans="8:9">
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SpiritCopyConfig.xlsx
+++ b/Excel/SpiritCopyConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -305,6 +310,72 @@
   </si>
   <si>
     <t>孙权</t>
+  </si>
+  <si>
+    <t>群雄·天级战场</t>
+  </si>
+  <si>
+    <t>于禁</t>
+  </si>
+  <si>
+    <t>群雄·地级战场</t>
+  </si>
+  <si>
+    <t>李典</t>
+  </si>
+  <si>
+    <t>10000000</t>
+  </si>
+  <si>
+    <t>12000000</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>群雄·玄级战场</t>
+  </si>
+  <si>
+    <t>张春华</t>
+  </si>
+  <si>
+    <t>30000000</t>
+  </si>
+  <si>
+    <t>群雄·黄级战场</t>
+  </si>
+  <si>
+    <t>蔡文姬</t>
+  </si>
+  <si>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>3600000</t>
+  </si>
+  <si>
+    <t>群雄·宇级战场</t>
+  </si>
+  <si>
+    <t>许诸</t>
+  </si>
+  <si>
+    <t>群雄·宙级战场</t>
+  </si>
+  <si>
+    <t>张辽</t>
+  </si>
+  <si>
+    <t>群雄·洪级战场</t>
+  </si>
+  <si>
+    <t>司马懿</t>
+  </si>
+  <si>
+    <t>群雄·荒级战场</t>
+  </si>
+  <si>
+    <t>曹操</t>
   </si>
 </sst>
 </file>
@@ -966,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -991,6 +1062,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
@@ -1534,10 +1608,10 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="16" t="s">
         <v>20</v>
       </c>
       <c r="J6" s="7">
@@ -1568,7 +1642,7 @@
       <c r="T6" s="2">
         <v>1000</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="U6" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1588,10 +1662,10 @@
       <c r="G7" s="1">
         <v>50</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="16" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="7">
@@ -1623,7 +1697,7 @@
       <c r="T7" s="2">
         <v>2000</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="U7" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1643,10 +1717,10 @@
       <c r="G8" s="1">
         <v>100</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="16" t="s">
         <v>29</v>
       </c>
       <c r="J8" s="7">
@@ -1678,7 +1752,7 @@
       <c r="T8" s="2">
         <v>4000</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="U8" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1698,10 +1772,10 @@
       <c r="G9" s="1">
         <v>200</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="16" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="7">
@@ -1733,7 +1807,7 @@
       <c r="T9" s="2">
         <v>8000</v>
       </c>
-      <c r="U9" s="15" t="s">
+      <c r="U9" s="16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1985,10 +2059,10 @@
       <c r="G15" s="1">
         <v>200</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="16" t="s">
         <v>45</v>
       </c>
       <c r="J15" s="7">
@@ -2019,7 +2093,7 @@
       <c r="T15" s="2">
         <v>1000</v>
       </c>
-      <c r="U15" s="15" t="s">
+      <c r="U15" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2039,10 +2113,10 @@
       <c r="G16" s="1">
         <v>450</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="16" t="s">
         <v>29</v>
       </c>
       <c r="J16" s="7">
@@ -2073,7 +2147,7 @@
       <c r="T16" s="2">
         <v>2000</v>
       </c>
-      <c r="U16" s="15" t="s">
+      <c r="U16" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2093,10 +2167,10 @@
       <c r="G17" s="1">
         <v>700</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="16" t="s">
         <v>50</v>
       </c>
       <c r="J17" s="7">
@@ -2127,7 +2201,7 @@
       <c r="T17" s="2">
         <v>4000</v>
       </c>
-      <c r="U17" s="15" t="s">
+      <c r="U17" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2147,10 +2221,10 @@
       <c r="G18" s="1">
         <v>900</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="16" t="s">
         <v>53</v>
       </c>
       <c r="J18" s="7">
@@ -2181,7 +2255,7 @@
       <c r="T18" s="2">
         <v>8000</v>
       </c>
-      <c r="U18" s="15" t="s">
+      <c r="U18" s="16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2430,10 +2504,10 @@
       <c r="G24" s="1">
         <v>900</v>
       </c>
-      <c r="H24" s="15" t="s">
+      <c r="H24" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="16" t="s">
         <v>65</v>
       </c>
       <c r="J24" s="7">
@@ -2464,7 +2538,7 @@
       <c r="T24" s="2">
         <v>1000</v>
       </c>
-      <c r="U24" s="15" t="s">
+      <c r="U24" s="16" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2484,10 +2558,10 @@
       <c r="G25" s="1">
         <v>1200</v>
       </c>
-      <c r="H25" s="15" t="s">
+      <c r="H25" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="16" t="s">
         <v>69</v>
       </c>
       <c r="J25" s="7">
@@ -2518,7 +2592,7 @@
       <c r="T25" s="2">
         <v>2000</v>
       </c>
-      <c r="U25" s="15" t="s">
+      <c r="U25" s="16" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2538,10 +2612,10 @@
       <c r="G26" s="1">
         <v>1600</v>
       </c>
-      <c r="H26" s="15" t="s">
+      <c r="H26" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="16" t="s">
         <v>73</v>
       </c>
       <c r="J26" s="7">
@@ -2572,7 +2646,7 @@
       <c r="T26" s="2">
         <v>4000</v>
       </c>
-      <c r="U26" s="15" t="s">
+      <c r="U26" s="16" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2592,10 +2666,10 @@
       <c r="G27" s="1">
         <v>2000</v>
       </c>
-      <c r="H27" s="15" t="s">
+      <c r="H27" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="16" t="s">
         <v>77</v>
       </c>
       <c r="J27" s="7">
@@ -2626,7 +2700,7 @@
       <c r="T27" s="2">
         <v>8000</v>
       </c>
-      <c r="U27" s="15" t="s">
+      <c r="U27" s="16" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2847,43 +2921,467 @@
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:21">
+      <c r="H32" s="7"/>
       <c r="I32" s="7"/>
-    </row>
-    <row r="36" customHeight="1" spans="8:9">
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" customHeight="1" spans="8:9">
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" customHeight="1" spans="8:9">
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" customHeight="1" spans="8:9">
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" customHeight="1" spans="8:9">
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" customHeight="1" spans="8:9">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="U32" s="7"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:21">
+      <c r="C33" s="1">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1">
+        <v>4</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="J33" s="7">
+        <f t="shared" ref="J33:J40" si="4">I33*S33*1200</f>
+        <v>21600000000</v>
+      </c>
+      <c r="K33" s="7">
+        <v>280</v>
+      </c>
+      <c r="L33" s="8">
+        <v>100</v>
+      </c>
+      <c r="M33" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N33" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O33" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P33" s="8">
+        <v>99</v>
+      </c>
+      <c r="S33" s="8">
+        <v>3</v>
+      </c>
+      <c r="T33" s="2">
+        <v>2000</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:21">
+      <c r="C34" s="1">
+        <v>26</v>
+      </c>
+      <c r="D34" s="1">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2400</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J34" s="7">
+        <f t="shared" si="4"/>
+        <v>86400000000</v>
+      </c>
+      <c r="K34" s="7">
+        <v>320</v>
+      </c>
+      <c r="L34" s="8">
+        <v>100</v>
+      </c>
+      <c r="M34" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N34" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O34" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P34" s="8">
+        <v>99</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="2">
+        <v>4000</v>
+      </c>
+      <c r="U34" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:21">
+      <c r="C35" s="1">
+        <v>27</v>
+      </c>
+      <c r="D35" s="1">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="1">
+        <v>2900</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="7">
+        <f t="shared" si="4"/>
+        <v>324000000000</v>
+      </c>
+      <c r="K35" s="7">
+        <v>360</v>
+      </c>
+      <c r="L35" s="8">
+        <v>100</v>
+      </c>
+      <c r="M35" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N35" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O35" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P35" s="8">
+        <v>99</v>
+      </c>
+      <c r="S35" s="8">
+        <v>9</v>
+      </c>
+      <c r="T35" s="2">
+        <v>8000</v>
+      </c>
+      <c r="U35" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:21">
+      <c r="C36" s="1">
+        <v>28</v>
+      </c>
+      <c r="D36" s="1">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="1">
+        <v>3400</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J36" s="7">
+        <f t="shared" si="4"/>
+        <v>1440000000000</v>
+      </c>
+      <c r="K36" s="7">
+        <v>400</v>
+      </c>
+      <c r="L36" s="8">
+        <v>100</v>
+      </c>
+      <c r="M36" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N36" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O36" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P36" s="8">
+        <v>99</v>
+      </c>
+      <c r="S36" s="8">
+        <v>12</v>
+      </c>
+      <c r="T36" s="2">
+        <v>16000</v>
+      </c>
+      <c r="U36" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:21">
+      <c r="C37" s="1">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1">
+        <v>4</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>240000000</v>
+      </c>
+      <c r="I37" s="7">
+        <v>250000000</v>
+      </c>
+      <c r="J37" s="7">
+        <f t="shared" si="4"/>
+        <v>4500000000000</v>
+      </c>
+      <c r="K37" s="7">
+        <v>400</v>
+      </c>
+      <c r="L37" s="8">
+        <v>100</v>
+      </c>
+      <c r="M37" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N37" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O37" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P37" s="8">
+        <v>99</v>
+      </c>
+      <c r="S37" s="8">
+        <v>15</v>
+      </c>
+      <c r="T37" s="2">
+        <v>30000</v>
+      </c>
+      <c r="U37" s="7">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:21">
+      <c r="C38" s="1">
+        <v>30</v>
+      </c>
+      <c r="D38" s="1">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G38" s="1">
+        <v>4500</v>
+      </c>
+      <c r="H38" s="7">
+        <v>500000000</v>
+      </c>
+      <c r="I38" s="7">
+        <v>500000000</v>
+      </c>
+      <c r="J38" s="7">
+        <f t="shared" si="4"/>
+        <v>10800000000000</v>
+      </c>
+      <c r="K38" s="7">
+        <v>400</v>
+      </c>
+      <c r="L38" s="8">
+        <v>100</v>
+      </c>
+      <c r="M38" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N38" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O38" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P38" s="8">
+        <v>99</v>
+      </c>
+      <c r="S38" s="8">
+        <v>18</v>
+      </c>
+      <c r="T38" s="2">
+        <v>50000</v>
+      </c>
+      <c r="U38" s="7">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:21">
+      <c r="C39" s="1">
+        <v>31</v>
+      </c>
+      <c r="D39" s="1">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="G39" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="I39" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="J39" s="7">
+        <f t="shared" si="4"/>
+        <v>25200000000000</v>
+      </c>
+      <c r="K39" s="7">
+        <v>400</v>
+      </c>
+      <c r="L39" s="8">
+        <v>100</v>
+      </c>
+      <c r="M39" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N39" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O39" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P39" s="8">
+        <v>99</v>
+      </c>
+      <c r="S39" s="8">
+        <v>21</v>
+      </c>
+      <c r="T39" s="2">
+        <v>70000</v>
+      </c>
+      <c r="U39" s="7">
+        <v>24000000</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:21">
+      <c r="C40" s="1">
+        <v>32</v>
+      </c>
+      <c r="D40" s="1">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5500</v>
+      </c>
+      <c r="H40" s="7">
+        <v>2500000000</v>
+      </c>
+      <c r="I40" s="7">
+        <v>2000000000</v>
+      </c>
+      <c r="J40" s="7">
+        <f t="shared" si="4"/>
+        <v>64800000000000</v>
+      </c>
+      <c r="K40" s="7">
+        <v>400</v>
+      </c>
+      <c r="L40" s="8">
+        <v>100</v>
+      </c>
+      <c r="M40" s="8">
+        <v>1800</v>
+      </c>
+      <c r="N40" s="8">
+        <v>1800</v>
+      </c>
+      <c r="O40" s="8">
+        <v>1800</v>
+      </c>
+      <c r="P40" s="8">
+        <v>99</v>
+      </c>
+      <c r="S40" s="8">
+        <v>27</v>
+      </c>
+      <c r="T40" s="2">
+        <v>100000</v>
+      </c>
+      <c r="U40" s="7">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:21">
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
     </row>
-    <row r="42" customHeight="1" spans="8:9">
+    <row r="42" customHeight="1" spans="3:21">
       <c r="H42" s="7"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" customHeight="1" spans="8:9">
+    <row r="43" customHeight="1" spans="3:21">
       <c r="H43" s="7"/>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" customHeight="1" spans="8:9">
+    <row r="44" customHeight="1" spans="3:21">
       <c r="H44" s="7"/>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" customHeight="1" spans="8:9">
+    <row r="45" customHeight="1" spans="3:21">
       <c r="H45" s="7"/>
       <c r="I45" s="7"/>
     </row>
